--- a/scripts/templates/career-sheet.xlsx
+++ b/scripts/templates/career-sheet.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10404"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D523C20-E49A-5747-A7A9-16D4A584914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460"/>
   </bookViews>
   <sheets>
-    <sheet name="スキルシート" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="スキルシート" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>職務経歴書</t>
   </si>
@@ -77,7 +76,7 @@
     <t>得意技術</t>
   </si>
   <si>
-    <t>フロントエンド	：{{skills.frontend|join:", "}}
+    <t xml:space="preserve">フロントエンド	：{{skills.frontend|join:", "}}
 バックエンド：{{skills.backend|join:", "}}
 インフラ：{{skills.infrastructure|join:", "}}
 AI：{{skills.ai|join:", "}}</t>
@@ -92,217 +91,215 @@
     <t>自己PR</t>
   </si>
   <si>
-    <t>期間</t>
-  </si>
-  <si>
-    <t>業務内容</t>
-  </si>
-  <si>
-    <t>役割
-規模</t>
-  </si>
-  <si>
-    <t>使用言語</t>
-  </si>
-  <si>
-    <t>DB</t>
-  </si>
-  <si>
-    <t>サーバOS</t>
-  </si>
-  <si>
-    <t>FW・MW
-ツール等</t>
-  </si>
-  <si>
-    <t>担当工程</t>
-  </si>
-  <si>
-    <t>要
-件
-定
-義</t>
-  </si>
-  <si>
-    <t>基
-本
-設
-計</t>
-  </si>
-  <si>
-    <t>詳
-細
-設
-計</t>
-  </si>
-  <si>
-    <t>実
-装
-・
-単
-体</t>
-  </si>
-  <si>
-    <t>結
-合
-テ
-ス
-ト</t>
-  </si>
-  <si>
-    <t>総
-合
-テ
-ス
-ト</t>
-  </si>
-  <si>
-    <t>保
-守
-・
-運
-用</t>
-  </si>
-  <si>
-    <t>{{#each projects}}</t>
-  </si>
-  <si>
-    <t>{{id}}</t>
-  </si>
-  <si>
-    <t>【{{contractType|default:"—"}}】 {{name}}</t>
-  </si>
-  <si>
-    <t>{{period.start}}
-|
-{{period.end}}
-({{monthCount}}ヶ月)</t>
-  </si>
-  <si>
-    <t>{{description ? "＜担当業務＞\n"+description+"\n\n" : ""}}{{learning ? "＜業務で得た知見＞\n"+learning+"\n\n" : ""}}{{comments ? "＜コメント＞\n"+comments+"\n\n" : ""}}</t>
-  </si>
-  <si>
-    <t>{{isLeader?"チームリーダー\n\n":""}}開発{{teamSize}}名  
-/  チーム{{projectSize}}名</t>
-  </si>
-  <si>
-    <t>{{languages}}</t>
-  </si>
-  <si>
-    <t>{{databases}}</t>
-  </si>
-  <si>
-    <t>{{serverOS}}</t>
-  </si>
-  <si>
-    <t>{{frameworks|join:"\n "}}</t>
-  </si>
-  <si>
-    <t>{{phase.requirementDefinition ? "●" : ""}}</t>
-  </si>
-  <si>
-    <t>{{phase.basicDesign ? "●" : ""}}</t>
-  </si>
-  <si>
-    <t>{{phase.detailedDesign ? "●" : ""}}</t>
-  </si>
-  <si>
-    <t>{{phase.implementation ? "●" : ""}}</t>
-  </si>
-  <si>
-    <t>{{phase.integrationTest ? "●" : ""}}</t>
-  </si>
-  <si>
-    <t>{{phase.systemTest ? "●" : ""}}</t>
-  </si>
-  <si>
-    <t>{{phase.maintenance ? "●" : ""}}</t>
-  </si>
-  <si>
-    <t>{{/each}}</t>
-  </si>
-  <si>
-    <t>＜自己PR＞
+    <t xml:space="preserve">＜自己PR＞
 {{selfPR.summary}}
 ＜経歴＞
 {{selfPR.careerHistory|join:"\n"}}
 Github: ogata-ryosuke
 プロジェクト一覧について：
 {{projectsDisclaimer}}</t>
-    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>AI活用レベル</t>
+  </si>
+  <si>
+    <t>{{aiUtilization.excelText}}</t>
+  </si>
+  <si>
+    <t>期間</t>
+  </si>
+  <si>
+    <t>業務内容</t>
+  </si>
+  <si>
+    <t xml:space="preserve">役割
+規模</t>
+  </si>
+  <si>
+    <t>使用言語</t>
+  </si>
+  <si>
+    <t>DB</t>
+  </si>
+  <si>
+    <t>サーバOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FW・MW
+ツール等</t>
+  </si>
+  <si>
+    <t>担当工程</t>
+  </si>
+  <si>
+    <t xml:space="preserve">要
+件
+定
+義</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基
+本
+設
+計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">詳
+細
+設
+計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実
+装
+・
+単
+体</t>
+  </si>
+  <si>
+    <t xml:space="preserve">結
+合
+テ
+ス
+ト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総
+合
+テ
+ス
+ト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保
+守
+・
+運
+用</t>
+  </si>
+  <si>
+    <t>{{#each projects}}</t>
+  </si>
+  <si>
+    <t>{{id}}</t>
+  </si>
+  <si>
+    <t>【{{contractType|default:"—"}}】 {{name}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{period.start}}
+|
+{{period.end}}
+({{monthCount}}ヶ月)</t>
+  </si>
+  <si>
+    <t>{{description ? "＜担当業務＞\n"+description+"\n\n" : ""}}{{learning ? "＜業務で得た知見＞\n"+learning+"\n\n" : ""}}{{comments ? "＜コメント＞\n"+comments+"\n\n" : ""}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{isLeader?"チームリーダー\n\n":""}}開発{{teamSize}}名  
+/  チーム{{projectSize}}名</t>
+  </si>
+  <si>
+    <t>{{languages}}</t>
+  </si>
+  <si>
+    <t>{{databases}}</t>
+  </si>
+  <si>
+    <t>{{serverOS}}</t>
+  </si>
+  <si>
+    <t>{{frameworks|join:"\n "}}</t>
+  </si>
+  <si>
+    <t>{{phase.requirementDefinition ? "●" : ""}}</t>
+  </si>
+  <si>
+    <t>{{phase.basicDesign ? "●" : ""}}</t>
+  </si>
+  <si>
+    <t>{{phase.detailedDesign ? "●" : ""}}</t>
+  </si>
+  <si>
+    <t>{{phase.implementation ? "●" : ""}}</t>
+  </si>
+  <si>
+    <t>{{phase.integrationTest ? "●" : ""}}</t>
+  </si>
+  <si>
+    <t>{{phase.systemTest ? "●" : ""}}</t>
+  </si>
+  <si>
+    <t>{{phase.maintenance ? "●" : ""}}</t>
+  </si>
+  <si>
+    <t>{{/each}}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="128"/>
+      <color rgb="FF008B8B"/>
+      <family val="2"/>
       <sz val="20"/>
-      <color rgb="FF008B8B"/>
       <name val="Meiryo"/>
-      <family val="2"/>
-      <charset val="128"/>
     </font>
     <font>
       <b/>
+      <charset val="128"/>
+      <color rgb="FFFFFFFF"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Meiryo"/>
-      <family val="2"/>
-      <charset val="128"/>
     </font>
     <font>
+      <charset val="128"/>
+      <color rgb="FF1A1A1A"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color rgb="FF1A1A1A"/>
       <name val="Meiryo"/>
-      <family val="2"/>
-      <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
     </font>
     <font>
       <b/>
+      <charset val="128"/>
+      <color rgb="FFFFFFFF"/>
+      <family val="2"/>
       <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Meiryo"/>
-      <family val="2"/>
-      <charset val="128"/>
     </font>
     <font>
       <b/>
+      <charset val="128"/>
+      <color rgb="FF1E40AF"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF1E40AF"/>
       <name val="Meiryo"/>
-      <family val="2"/>
-      <charset val="128"/>
     </font>
     <font>
+      <charset val="128"/>
+      <color rgb="FF1A1A1A"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FF1A1A1A"/>
       <name val="Meiryo"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -355,8 +352,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -366,6 +366,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -376,31 +377,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -736,9 +727,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -750,396 +741,418 @@
     <col min="9" max="15" width="3.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="53.25" customHeight="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" ht="53.25" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-    </row>
-    <row r="2" spans="1:15" ht="46.75" customHeight="1">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" ht="46.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-    </row>
-    <row r="3" spans="1:15" ht="46.75" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" ht="46.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-    </row>
-    <row r="4" spans="1:15" ht="70.75" customHeight="1">
-      <c r="A4" s="11" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" ht="70.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-    </row>
-    <row r="5" spans="1:15" ht="46.75" customHeight="1">
-      <c r="A5" s="11" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" ht="46.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-    </row>
-    <row r="6" spans="1:15" ht="118.75" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" ht="118.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-    </row>
-    <row r="7" spans="1:15" ht="83" customHeight="1">
-      <c r="A7" s="11" t="s">
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" ht="83" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-    </row>
-    <row r="8" spans="1:15" ht="87" customHeight="1">
-      <c r="A8" s="11" t="s">
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" ht="87" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-    </row>
-    <row r="9" spans="1:15" ht="306" customHeight="1">
-      <c r="A9" s="11" t="s">
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" ht="306" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" ht="250" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="12" ht="40" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" ht="120" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+    </row>
+    <row r="15" ht="33.25" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+    </row>
+    <row r="16" ht="323" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="N16" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-    </row>
-    <row r="11" spans="1:15" ht="40" customHeight="1">
-      <c r="A11" s="15"/>
-      <c r="B11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-    </row>
-    <row r="12" spans="1:15" ht="120" customHeight="1">
-      <c r="A12" s="15"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="17" customHeight="1">
-      <c r="A13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-    </row>
-    <row r="14" spans="1:15" ht="33.25" customHeight="1">
-      <c r="A14" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-    </row>
-    <row r="15" spans="1:15" ht="323" customHeight="1">
-      <c r="A15" s="14"/>
-      <c r="B15" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" t="s">
-        <v>56</v>
+      <c r="O16" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="B14:O14"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="I11:O11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
+  <mergeCells count="30">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="E2:O2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="E3:O3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="E4:O4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:O5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:O6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:O7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:O8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:O9"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="E4:O4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:O5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:O6"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="E2:O2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="E3:O3"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:O10"/>
+    <mergeCell ref="I12:O12"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="B15:O15"/>
+    <mergeCell ref="A15:A16"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>